--- a/output_phyto/phyto_Intermediate_andersen_1999.xlsx
+++ b/output_phyto/phyto_Intermediate_andersen_1999.xlsx
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">10.1007/978-3-642-58646-0_19</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_andersen_1999.xlsx</t>
+    <t xml:space="preserve">phytoplankton_andersen_1999_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">alkenone unsaturation</t>
+    <t xml:space="preserve">published Uk37 temperature</t>
   </si>
   <si>
     <t xml:space="preserve">WOA_94</t>
@@ -1585,7 +1585,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1651,12 +1651,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1770,7 +1764,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1869,7 +1863,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2595,7 +2588,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2613,8 +2606,8 @@
       <c r="H5" t="n">
         <v>0.0013</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2632,7 +2625,7 @@
         <v>-23.48</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08</v>
+        <v>0.0565685424949238</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2643,8 +2636,8 @@
       <c r="R5" s="11" t="n">
         <v>25.1</v>
       </c>
-      <c r="S5" t="e">
-        <v>#N/A</v>
+      <c r="S5" t="n">
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2661,29 +2654,29 @@
       <c r="X5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z5" t="e">
-        <v>#N/A</v>
+      <c r="Y5" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA5" t="s">
         <v>278</v>
       </c>
-      <c r="AB5" t="e">
-        <v>#N/A</v>
+      <c r="AB5" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF5" t="e">
-        <v>#N/A</v>
+      <c r="AD5" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG5" t="e">
         <v>#N/A</v>
@@ -2705,7 +2698,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2723,8 +2716,8 @@
       <c r="H6" t="n">
         <v>0.006</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2742,7 +2735,7 @@
         <v>-23.64</v>
       </c>
       <c r="O6" t="n">
-        <v>0.34</v>
+        <v>0.196299091524473</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2753,8 +2746,8 @@
       <c r="R6" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="S6" t="e">
-        <v>#N/A</v>
+      <c r="S6" t="n">
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2771,29 +2764,29 @@
       <c r="X6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z6" t="e">
-        <v>#N/A</v>
+      <c r="Y6" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA6" t="s">
         <v>278</v>
       </c>
-      <c r="AB6" t="e">
-        <v>#N/A</v>
+      <c r="AB6" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF6" t="e">
-        <v>#N/A</v>
+      <c r="AD6" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG6" t="e">
         <v>#N/A</v>
@@ -2815,7 +2808,7 @@
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2833,8 +2826,8 @@
       <c r="H7" t="n">
         <v>0.0082</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2852,7 +2845,7 @@
         <v>-24.15</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4</v>
+        <v>0.178885438199983</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2863,8 +2856,8 @@
       <c r="R7" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="S7" t="e">
-        <v>#N/A</v>
+      <c r="S7" t="n">
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -2881,29 +2874,29 @@
       <c r="X7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z7" t="e">
-        <v>#N/A</v>
+      <c r="Y7" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA7" t="s">
         <v>278</v>
       </c>
-      <c r="AB7" t="e">
-        <v>#N/A</v>
+      <c r="AB7" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF7" t="e">
-        <v>#N/A</v>
+      <c r="AD7" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG7" t="e">
         <v>#N/A</v>
@@ -2925,7 +2918,7 @@
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -2943,8 +2936,8 @@
       <c r="H8" t="n">
         <v>0.0112</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2962,7 +2955,7 @@
         <v>-23.96</v>
       </c>
       <c r="O8" t="n">
-        <v>0.52</v>
+        <v>0.367695526217005</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -2973,8 +2966,8 @@
       <c r="R8" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="S8" t="e">
-        <v>#N/A</v>
+      <c r="S8" t="n">
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -2991,29 +2984,29 @@
       <c r="X8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z8" t="e">
-        <v>#N/A</v>
+      <c r="Y8" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA8" t="s">
         <v>278</v>
       </c>
-      <c r="AB8" t="e">
-        <v>#N/A</v>
+      <c r="AB8" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF8" t="e">
-        <v>#N/A</v>
+      <c r="AD8" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG8" t="e">
         <v>#N/A</v>
@@ -3035,7 +3028,7 @@
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3053,8 +3046,8 @@
       <c r="H9" t="n">
         <v>0.0178</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3072,7 +3065,7 @@
         <v>-24.32</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02</v>
+        <v>0.0141421356237309</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3083,8 +3076,8 @@
       <c r="R9" s="11" t="n">
         <v>21.7</v>
       </c>
-      <c r="S9" t="e">
-        <v>#N/A</v>
+      <c r="S9" t="n">
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3101,29 +3094,29 @@
       <c r="X9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z9" t="e">
-        <v>#N/A</v>
+      <c r="Y9" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA9" t="s">
         <v>278</v>
       </c>
-      <c r="AB9" t="e">
-        <v>#N/A</v>
+      <c r="AB9" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF9" t="e">
-        <v>#N/A</v>
+      <c r="AD9" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG9" t="e">
         <v>#N/A</v>
@@ -3145,7 +3138,7 @@
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3163,8 +3156,8 @@
       <c r="H10" t="n">
         <v>0.0196</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.004</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3182,7 +3175,7 @@
         <v>-24.04</v>
       </c>
       <c r="O10" t="n">
-        <v>0.62</v>
+        <v>0.357957166897568</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3193,8 +3186,8 @@
       <c r="R10" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="S10" t="e">
-        <v>#N/A</v>
+      <c r="S10" t="n">
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3211,29 +3204,29 @@
       <c r="X10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z10" t="e">
-        <v>#N/A</v>
+      <c r="Y10" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA10" t="s">
         <v>278</v>
       </c>
-      <c r="AB10" t="e">
-        <v>#N/A</v>
+      <c r="AB10" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF10" t="e">
-        <v>#N/A</v>
+      <c r="AD10" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG10" t="e">
         <v>#N/A</v>
@@ -3255,7 +3248,7 @@
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3273,8 +3266,8 @@
       <c r="H11" t="n">
         <v>0.0255</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.004</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3292,7 +3285,7 @@
         <v>-24.16</v>
       </c>
       <c r="O11" t="n">
-        <v>0.68</v>
+        <v>0.34</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3303,8 +3296,8 @@
       <c r="R11" s="11" t="n">
         <v>22.1</v>
       </c>
-      <c r="S11" t="e">
-        <v>#N/A</v>
+      <c r="S11" t="n">
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3321,29 +3314,29 @@
       <c r="X11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z11" t="e">
-        <v>#N/A</v>
+      <c r="Y11" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA11" t="s">
         <v>278</v>
       </c>
-      <c r="AB11" t="e">
-        <v>#N/A</v>
+      <c r="AB11" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC11" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF11" t="e">
-        <v>#N/A</v>
+      <c r="AD11" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG11" t="e">
         <v>#N/A</v>
@@ -3365,7 +3358,7 @@
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3383,8 +3376,8 @@
       <c r="H12" t="n">
         <v>0.0349</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.004</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3402,7 +3395,7 @@
         <v>-23.2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06</v>
+        <v>0.0346410161513775</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3413,8 +3406,8 @@
       <c r="R12" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="S12" t="e">
-        <v>#N/A</v>
+      <c r="S12" t="n">
+        <v>3</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3431,29 +3424,29 @@
       <c r="X12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z12" t="e">
-        <v>#N/A</v>
+      <c r="Y12" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA12" t="s">
         <v>278</v>
       </c>
-      <c r="AB12" t="e">
-        <v>#N/A</v>
+      <c r="AB12" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF12" t="e">
-        <v>#N/A</v>
+      <c r="AD12" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG12" t="e">
         <v>#N/A</v>
@@ -3475,7 +3468,7 @@
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3493,8 +3486,8 @@
       <c r="H13" t="n">
         <v>0.0474</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.004</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3512,7 +3505,7 @@
         <v>-23.3</v>
       </c>
       <c r="O13" t="n">
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3523,8 +3516,8 @@
       <c r="R13" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="S13" t="e">
-        <v>#N/A</v>
+      <c r="S13" t="n">
+        <v>3</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3541,29 +3534,29 @@
       <c r="X13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z13" t="e">
-        <v>#N/A</v>
+      <c r="Y13" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA13" t="s">
         <v>278</v>
       </c>
-      <c r="AB13" t="e">
-        <v>#N/A</v>
+      <c r="AB13" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF13" t="e">
-        <v>#N/A</v>
+      <c r="AD13" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG13" t="e">
         <v>#N/A</v>
@@ -3585,7 +3578,7 @@
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3603,8 +3596,8 @@
       <c r="H14" t="n">
         <v>0.0474</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.004</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3622,7 +3615,7 @@
         <v>-23.39</v>
       </c>
       <c r="O14" t="n">
-        <v>0.32</v>
+        <v>0.143108350559987</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3633,8 +3626,8 @@
       <c r="R14" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="S14" t="e">
-        <v>#N/A</v>
+      <c r="S14" t="n">
+        <v>3</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3651,29 +3644,29 @@
       <c r="X14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z14" t="e">
-        <v>#N/A</v>
+      <c r="Y14" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA14" t="s">
         <v>278</v>
       </c>
-      <c r="AB14" t="e">
-        <v>#N/A</v>
+      <c r="AB14" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF14" t="e">
-        <v>#N/A</v>
+      <c r="AD14" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG14" t="e">
         <v>#N/A</v>
@@ -3695,7 +3688,7 @@
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3713,8 +3706,8 @@
       <c r="H15" t="n">
         <v>0.0592</v>
       </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+      <c r="I15" t="n">
+        <v>0.004</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3732,7 +3725,7 @@
         <v>-23.43</v>
       </c>
       <c r="O15" t="n">
-        <v>0.64</v>
+        <v>0.369504172281361</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3743,8 +3736,8 @@
       <c r="R15" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="S15" t="e">
-        <v>#N/A</v>
+      <c r="S15" t="n">
+        <v>3</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -3761,29 +3754,29 @@
       <c r="X15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z15" t="e">
-        <v>#N/A</v>
+      <c r="Y15" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA15" t="s">
         <v>278</v>
       </c>
-      <c r="AB15" t="e">
-        <v>#N/A</v>
+      <c r="AB15" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF15" t="e">
-        <v>#N/A</v>
+      <c r="AD15" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG15" t="e">
         <v>#N/A</v>
@@ -3805,7 +3798,7 @@
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3823,8 +3816,8 @@
       <c r="H16" t="n">
         <v>0.0647</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.004</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3842,7 +3835,7 @@
         <v>-23.41</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.707106781186547</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3853,8 +3846,8 @@
       <c r="R16" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="S16" t="e">
-        <v>#N/A</v>
+      <c r="S16" t="n">
+        <v>3</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -3871,29 +3864,29 @@
       <c r="X16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z16" t="e">
-        <v>#N/A</v>
+      <c r="Y16" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA16" t="s">
         <v>278</v>
       </c>
-      <c r="AB16" t="e">
-        <v>#N/A</v>
+      <c r="AB16" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF16" t="e">
-        <v>#N/A</v>
+      <c r="AD16" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG16" t="e">
         <v>#N/A</v>
@@ -3915,7 +3908,7 @@
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -3933,8 +3926,8 @@
       <c r="H17" t="n">
         <v>0.0693</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.004</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3952,7 +3945,7 @@
         <v>-23.67</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5</v>
+        <v>0.353553390593274</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -3963,8 +3956,8 @@
       <c r="R17" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="S17" t="e">
-        <v>#N/A</v>
+      <c r="S17" t="n">
+        <v>3</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -3981,29 +3974,29 @@
       <c r="X17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z17" t="e">
-        <v>#N/A</v>
+      <c r="Y17" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA17" t="s">
         <v>278</v>
       </c>
-      <c r="AB17" t="e">
-        <v>#N/A</v>
+      <c r="AB17" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF17" t="e">
-        <v>#N/A</v>
+      <c r="AD17" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG17" t="e">
         <v>#N/A</v>
@@ -4025,7 +4018,7 @@
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4043,8 +4036,8 @@
       <c r="H18" t="n">
         <v>0.0693</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.004</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4062,7 +4055,7 @@
         <v>-24.38</v>
       </c>
       <c r="O18" t="n">
-        <v>0.44</v>
+        <v>0.254034118443435</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4073,8 +4066,8 @@
       <c r="R18" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="S18" t="e">
-        <v>#N/A</v>
+      <c r="S18" t="n">
+        <v>3</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4091,29 +4084,29 @@
       <c r="X18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z18" t="e">
-        <v>#N/A</v>
+      <c r="Y18" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA18" t="s">
         <v>278</v>
       </c>
-      <c r="AB18" t="e">
-        <v>#N/A</v>
+      <c r="AB18" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF18" t="e">
-        <v>#N/A</v>
+      <c r="AD18" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG18" t="e">
         <v>#N/A</v>
@@ -4135,7 +4128,7 @@
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4153,8 +4146,8 @@
       <c r="H19" t="n">
         <v>0.0785</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.004</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4172,7 +4165,7 @@
         <v>-24.2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4183,8 +4176,8 @@
       <c r="R19" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="S19" t="e">
-        <v>#N/A</v>
+      <c r="S19" t="n">
+        <v>3</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4201,29 +4194,29 @@
       <c r="X19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z19" t="e">
-        <v>#N/A</v>
+      <c r="Y19" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA19" t="s">
         <v>278</v>
       </c>
-      <c r="AB19" t="e">
-        <v>#N/A</v>
+      <c r="AB19" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF19" t="e">
-        <v>#N/A</v>
+      <c r="AD19" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG19" t="e">
         <v>#N/A</v>
@@ -4245,7 +4238,7 @@
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4263,8 +4256,8 @@
       <c r="H20" t="n">
         <v>0.08</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.004</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4282,7 +4275,7 @@
         <v>-23.62</v>
       </c>
       <c r="O20" t="n">
-        <v>0.14</v>
+        <v>0.0808290376865476</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4293,8 +4286,8 @@
       <c r="R20" s="11" t="n">
         <v>24.4</v>
       </c>
-      <c r="S20" t="e">
-        <v>#N/A</v>
+      <c r="S20" t="n">
+        <v>3</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4311,29 +4304,29 @@
       <c r="X20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z20" t="e">
-        <v>#N/A</v>
+      <c r="Y20" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA20" t="s">
         <v>278</v>
       </c>
-      <c r="AB20" t="e">
-        <v>#N/A</v>
+      <c r="AB20" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF20" t="e">
-        <v>#N/A</v>
+      <c r="AD20" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG20" t="e">
         <v>#N/A</v>
@@ -4355,7 +4348,7 @@
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4373,8 +4366,8 @@
       <c r="H21" t="n">
         <v>0.084</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.004</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4392,7 +4385,7 @@
         <v>-23.04</v>
       </c>
       <c r="O21" t="n">
-        <v>0.64</v>
+        <v>0.45254833995939</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4403,8 +4396,8 @@
       <c r="R21" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="S21" t="e">
-        <v>#N/A</v>
+      <c r="S21" t="n">
+        <v>3</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4421,29 +4414,29 @@
       <c r="X21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z21" t="e">
-        <v>#N/A</v>
+      <c r="Y21" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA21" t="s">
         <v>278</v>
       </c>
-      <c r="AB21" t="e">
-        <v>#N/A</v>
+      <c r="AB21" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF21" t="e">
-        <v>#N/A</v>
+      <c r="AD21" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG21" t="e">
         <v>#N/A</v>
@@ -4465,7 +4458,7 @@
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4483,8 +4476,8 @@
       <c r="H22" t="n">
         <v>0.087</v>
       </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+      <c r="I22" t="n">
+        <v>0.004</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4502,7 +4495,7 @@
         <v>-22.93</v>
       </c>
       <c r="O22" t="n">
-        <v>0.68</v>
+        <v>0.392598183048946</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4513,8 +4506,8 @@
       <c r="R22" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="S22" t="e">
-        <v>#N/A</v>
+      <c r="S22" t="n">
+        <v>3</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4531,29 +4524,29 @@
       <c r="X22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z22" t="e">
-        <v>#N/A</v>
+      <c r="Y22" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA22" t="s">
         <v>278</v>
       </c>
-      <c r="AB22" t="e">
-        <v>#N/A</v>
+      <c r="AB22" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF22" t="e">
-        <v>#N/A</v>
+      <c r="AD22" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG22" t="e">
         <v>#N/A</v>
@@ -4575,7 +4568,7 @@
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4593,8 +4586,8 @@
       <c r="H23" t="n">
         <v>0.1</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.004</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4612,7 +4605,7 @@
         <v>-24.18</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4623,8 +4616,8 @@
       <c r="R23" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="S23" t="e">
-        <v>#N/A</v>
+      <c r="S23" t="n">
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4641,29 +4634,29 @@
       <c r="X23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z23" t="e">
-        <v>#N/A</v>
+      <c r="Y23" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA23" t="s">
         <v>278</v>
       </c>
-      <c r="AB23" t="e">
-        <v>#N/A</v>
+      <c r="AB23" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF23" t="e">
-        <v>#N/A</v>
+      <c r="AD23" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG23" t="e">
         <v>#N/A</v>
@@ -4685,7 +4678,7 @@
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4703,8 +4696,8 @@
       <c r="H24" t="n">
         <v>0.1126</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.004</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4722,7 +4715,7 @@
         <v>-24.28</v>
       </c>
       <c r="O24" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4733,8 +4726,8 @@
       <c r="R24" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="S24" t="e">
-        <v>#N/A</v>
+      <c r="S24" t="n">
+        <v>3</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -4751,29 +4744,29 @@
       <c r="X24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z24" t="e">
-        <v>#N/A</v>
+      <c r="Y24" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA24" t="s">
         <v>278</v>
       </c>
-      <c r="AB24" t="e">
-        <v>#N/A</v>
+      <c r="AB24" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF24" t="e">
-        <v>#N/A</v>
+      <c r="AD24" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG24" t="e">
         <v>#N/A</v>
@@ -4795,7 +4788,7 @@
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -4813,8 +4806,8 @@
       <c r="H25" t="n">
         <v>0.1183</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.004</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4832,7 +4825,7 @@
         <v>-23.55</v>
       </c>
       <c r="O25" t="n">
-        <v>0.78</v>
+        <v>0.39</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4843,8 +4836,8 @@
       <c r="R25" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="S25" t="e">
-        <v>#N/A</v>
+      <c r="S25" t="n">
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -4861,29 +4854,29 @@
       <c r="X25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" t="e">
-        <v>#N/A</v>
+      <c r="Y25" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA25" t="s">
         <v>278</v>
       </c>
-      <c r="AB25" t="e">
-        <v>#N/A</v>
+      <c r="AB25" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" t="e">
-        <v>#N/A</v>
+      <c r="AD25" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG25" t="e">
         <v>#N/A</v>
@@ -4905,7 +4898,7 @@
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -4923,8 +4916,8 @@
       <c r="H26" t="n">
         <v>0.1238</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.004</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4942,7 +4935,7 @@
         <v>-23.92</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2</v>
+        <v>0.115470053837925</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -4953,8 +4946,8 @@
       <c r="R26" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="S26" t="e">
-        <v>#N/A</v>
+      <c r="S26" t="n">
+        <v>3</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -4971,29 +4964,29 @@
       <c r="X26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z26" t="e">
-        <v>#N/A</v>
+      <c r="Y26" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA26" t="s">
         <v>278</v>
       </c>
-      <c r="AB26" t="e">
-        <v>#N/A</v>
+      <c r="AB26" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF26" t="e">
-        <v>#N/A</v>
+      <c r="AD26" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG26" t="e">
         <v>#N/A</v>
@@ -5015,7 +5008,7 @@
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5033,8 +5026,8 @@
       <c r="H27" t="n">
         <v>0.1273</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.004</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5052,7 +5045,7 @@
         <v>-25.15</v>
       </c>
       <c r="O27" t="n">
-        <v>0.16</v>
+        <v>0.0923760430703401</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5063,8 +5056,8 @@
       <c r="R27" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="S27" t="e">
-        <v>#N/A</v>
+      <c r="S27" t="n">
+        <v>3</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -5081,29 +5074,29 @@
       <c r="X27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z27" t="e">
-        <v>#N/A</v>
+      <c r="Y27" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA27" t="s">
         <v>278</v>
       </c>
-      <c r="AB27" t="e">
-        <v>#N/A</v>
+      <c r="AB27" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF27" t="e">
-        <v>#N/A</v>
+      <c r="AD27" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG27" t="e">
         <v>#N/A</v>
@@ -5125,7 +5118,7 @@
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5143,8 +5136,8 @@
       <c r="H28" t="n">
         <v>0.1343</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.004</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5162,7 +5155,7 @@
         <v>-24.05</v>
       </c>
       <c r="O28" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5173,8 +5166,8 @@
       <c r="R28" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="S28" t="e">
-        <v>#N/A</v>
+      <c r="S28" t="n">
+        <v>3</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -5191,29 +5184,29 @@
       <c r="X28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z28" t="e">
-        <v>#N/A</v>
+      <c r="Y28" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA28" t="s">
         <v>278</v>
       </c>
-      <c r="AB28" t="e">
-        <v>#N/A</v>
+      <c r="AB28" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF28" t="e">
-        <v>#N/A</v>
+      <c r="AD28" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG28" t="e">
         <v>#N/A</v>
@@ -5235,7 +5228,7 @@
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5253,8 +5246,8 @@
       <c r="H29" t="n">
         <v>0.1471</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.004</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5272,7 +5265,7 @@
         <v>-23.93</v>
       </c>
       <c r="O29" t="n">
-        <v>0.24</v>
+        <v>0.13856406460551</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5283,8 +5276,8 @@
       <c r="R29" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="S29" t="e">
-        <v>#N/A</v>
+      <c r="S29" t="n">
+        <v>3</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -5301,29 +5294,29 @@
       <c r="X29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z29" t="e">
-        <v>#N/A</v>
+      <c r="Y29" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA29" t="s">
         <v>278</v>
       </c>
-      <c r="AB29" t="e">
-        <v>#N/A</v>
+      <c r="AB29" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF29" t="e">
-        <v>#N/A</v>
+      <c r="AD29" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG29" t="e">
         <v>#N/A</v>
@@ -5345,7 +5338,7 @@
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5363,8 +5356,8 @@
       <c r="H30" t="n">
         <v>0.1502</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.004</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5382,7 +5375,7 @@
         <v>-24.19</v>
       </c>
       <c r="O30" t="n">
-        <v>0.34</v>
+        <v>0.240416305603426</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5393,8 +5386,8 @@
       <c r="R30" s="11" t="n">
         <v>21.7</v>
       </c>
-      <c r="S30" t="e">
-        <v>#N/A</v>
+      <c r="S30" t="n">
+        <v>3</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -5411,29 +5404,29 @@
       <c r="X30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z30" t="e">
-        <v>#N/A</v>
+      <c r="Y30" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA30" t="s">
         <v>278</v>
       </c>
-      <c r="AB30" t="e">
-        <v>#N/A</v>
+      <c r="AB30" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF30" t="e">
-        <v>#N/A</v>
+      <c r="AD30" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG30" t="e">
         <v>#N/A</v>
@@ -5455,7 +5448,7 @@
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5473,8 +5466,8 @@
       <c r="H31" t="n">
         <v>0.1603</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.004</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5492,7 +5485,7 @@
         <v>-25.19</v>
       </c>
       <c r="O31" t="n">
-        <v>0.92</v>
+        <v>0.650538238691624</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5503,8 +5496,8 @@
       <c r="R31" s="11" t="n">
         <v>23.6</v>
       </c>
-      <c r="S31" t="e">
-        <v>#N/A</v>
+      <c r="S31" t="n">
+        <v>3</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -5521,29 +5514,29 @@
       <c r="X31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z31" t="e">
-        <v>#N/A</v>
+      <c r="Y31" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA31" t="s">
         <v>278</v>
       </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="e">
         <v>#N/A</v>
@@ -5565,7 +5558,7 @@
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5583,8 +5576,8 @@
       <c r="H32" t="n">
         <v>0.1603</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.004</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5602,7 +5595,7 @@
         <v>-24.97</v>
       </c>
       <c r="O32" t="n">
-        <v>0.64</v>
+        <v>0.45254833995939</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5613,8 +5606,8 @@
       <c r="R32" s="11" t="n">
         <v>23.6</v>
       </c>
-      <c r="S32" t="e">
-        <v>#N/A</v>
+      <c r="S32" t="n">
+        <v>3</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -5631,29 +5624,29 @@
       <c r="X32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z32" t="e">
-        <v>#N/A</v>
+      <c r="Y32" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA32" t="s">
         <v>278</v>
       </c>
-      <c r="AB32" t="e">
-        <v>#N/A</v>
+      <c r="AB32" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF32" t="e">
-        <v>#N/A</v>
+      <c r="AD32" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG32" t="e">
         <v>#N/A</v>
@@ -5675,7 +5668,7 @@
       <c r="B33" t="s">
         <v>271</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" t="s">
         <v>272</v>
       </c>
       <c r="D33" t="s">
@@ -5693,8 +5686,8 @@
       <c r="H33" t="n">
         <v>0.171</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.004</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -5712,7 +5705,7 @@
         <v>-24.33</v>
       </c>
       <c r="O33" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -5723,8 +5716,8 @@
       <c r="R33" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="S33" t="e">
-        <v>#N/A</v>
+      <c r="S33" t="n">
+        <v>3</v>
       </c>
       <c r="T33" t="e">
         <v>#N/A</v>
@@ -5741,29 +5734,29 @@
       <c r="X33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z33" t="e">
-        <v>#N/A</v>
+      <c r="Y33" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA33" t="s">
         <v>278</v>
       </c>
-      <c r="AB33" t="e">
-        <v>#N/A</v>
+      <c r="AB33" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF33" t="e">
-        <v>#N/A</v>
+      <c r="AD33" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG33" t="e">
         <v>#N/A</v>
@@ -5785,7 +5778,7 @@
       <c r="B34" t="s">
         <v>271</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" t="s">
         <v>272</v>
       </c>
       <c r="D34" t="s">
@@ -5803,8 +5796,8 @@
       <c r="H34" t="n">
         <v>0.1817</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.004</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -5822,7 +5815,7 @@
         <v>-23.95</v>
       </c>
       <c r="O34" t="n">
-        <v>0.5</v>
+        <v>0.353553390593274</v>
       </c>
       <c r="P34" t="e">
         <v>#N/A</v>
@@ -5833,8 +5826,8 @@
       <c r="R34" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="S34" t="e">
-        <v>#N/A</v>
+      <c r="S34" t="n">
+        <v>3</v>
       </c>
       <c r="T34" t="e">
         <v>#N/A</v>
@@ -5851,29 +5844,29 @@
       <c r="X34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z34" t="e">
-        <v>#N/A</v>
+      <c r="Y34" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA34" t="s">
         <v>278</v>
       </c>
-      <c r="AB34" t="e">
-        <v>#N/A</v>
+      <c r="AB34" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF34" t="e">
-        <v>#N/A</v>
+      <c r="AD34" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG34" t="e">
         <v>#N/A</v>
@@ -5895,7 +5888,7 @@
       <c r="B35" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" t="s">
         <v>272</v>
       </c>
       <c r="D35" t="s">
@@ -5913,8 +5906,8 @@
       <c r="H35" t="n">
         <v>0.1817</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.004</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -5932,7 +5925,7 @@
         <v>-24.16</v>
       </c>
       <c r="O35" t="n">
-        <v>0.84</v>
+        <v>0.484974226119286</v>
       </c>
       <c r="P35" t="e">
         <v>#N/A</v>
@@ -5943,8 +5936,8 @@
       <c r="R35" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" t="e">
-        <v>#N/A</v>
+      <c r="S35" t="n">
+        <v>3</v>
       </c>
       <c r="T35" t="e">
         <v>#N/A</v>
@@ -5961,29 +5954,29 @@
       <c r="X35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z35" t="e">
-        <v>#N/A</v>
+      <c r="Y35" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA35" t="s">
         <v>278</v>
       </c>
-      <c r="AB35" t="e">
-        <v>#N/A</v>
+      <c r="AB35" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF35" t="e">
-        <v>#N/A</v>
+      <c r="AD35" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG35" t="e">
         <v>#N/A</v>
@@ -6005,7 +5998,7 @@
       <c r="B36" t="s">
         <v>271</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" t="s">
         <v>272</v>
       </c>
       <c r="D36" t="s">
@@ -6023,8 +6016,8 @@
       <c r="H36" t="n">
         <v>0.1837</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.004</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -6042,7 +6035,7 @@
         <v>-23.64</v>
       </c>
       <c r="O36" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="P36" t="e">
         <v>#N/A</v>
@@ -6053,8 +6046,8 @@
       <c r="R36" s="11" t="n">
         <v>24.2</v>
       </c>
-      <c r="S36" t="e">
-        <v>#N/A</v>
+      <c r="S36" t="n">
+        <v>3</v>
       </c>
       <c r="T36" t="e">
         <v>#N/A</v>
@@ -6071,29 +6064,29 @@
       <c r="X36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z36" t="e">
-        <v>#N/A</v>
+      <c r="Y36" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA36" t="s">
         <v>278</v>
       </c>
-      <c r="AB36" t="e">
-        <v>#N/A</v>
+      <c r="AB36" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF36" t="e">
-        <v>#N/A</v>
+      <c r="AD36" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG36" t="e">
         <v>#N/A</v>
@@ -6115,7 +6108,7 @@
       <c r="B37" t="s">
         <v>271</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" t="s">
         <v>272</v>
       </c>
       <c r="D37" t="s">
@@ -6133,8 +6126,8 @@
       <c r="H37" t="n">
         <v>0.1962</v>
       </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+      <c r="I37" t="n">
+        <v>0.004</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -6152,7 +6145,7 @@
         <v>-24.77</v>
       </c>
       <c r="O37" t="n">
-        <v>0.6</v>
+        <v>0.346410161513775</v>
       </c>
       <c r="P37" t="e">
         <v>#N/A</v>
@@ -6163,8 +6156,8 @@
       <c r="R37" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="S37" t="e">
-        <v>#N/A</v>
+      <c r="S37" t="n">
+        <v>3</v>
       </c>
       <c r="T37" t="e">
         <v>#N/A</v>
@@ -6181,29 +6174,29 @@
       <c r="X37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Y37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z37" t="e">
-        <v>#N/A</v>
+      <c r="Y37" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.534</v>
       </c>
       <c r="AA37" t="s">
         <v>278</v>
       </c>
-      <c r="AB37" t="e">
-        <v>#N/A</v>
+      <c r="AB37" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF37" t="e">
-        <v>#N/A</v>
+      <c r="AD37" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG37" t="e">
         <v>#N/A</v>
@@ -6500,41 +6493,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
